--- a/e2e/fixtures/assets-mixed.xlsx
+++ b/e2e/fixtures/assets-mixed.xlsx
@@ -22,6 +22,9 @@
     <t>Model</t>
   </si>
   <si>
+    <t>Brand</t>
+  </si>
+  <si>
     <t>Serial</t>
   </si>
   <si>
@@ -49,9 +52,18 @@
     <t>Warranty until</t>
   </si>
   <si>
+    <t>Loan until</t>
+  </si>
+  <si>
     <t>Vendor</t>
   </si>
   <si>
+    <t>Provenance</t>
+  </si>
+  <si>
+    <t>Invoice / receipt no.</t>
+  </si>
+  <si>
     <t>RMA ref</t>
   </si>
   <si>
@@ -71,6 +83,9 @@
   </si>
   <si>
     <t>USB-C Dock</t>
+  </si>
+  <si>
+    <t>Registered directly</t>
   </si>
   <si>
     <t>BR-PH-9102</t>
@@ -191,19 +206,23 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
+    <col min="19" max="19" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -252,134 +271,170 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
         <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="2"/>
-      <c r="M4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
       <c r="O7" t="s">
-        <v>37</v>
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
